--- a/automated.xlsx
+++ b/automated.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/dibendu/Documents/atp_analysis/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/dibendu/Documents/GitHub/Fit_repo/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4348F908-1B2F-4145-B058-B8784533C225}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A36B04A-7951-2744-BF74-288ED39F337D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1360" yWindow="4700" windowWidth="24540" windowHeight="14940" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -319,136 +319,40 @@
       <c r="A2">
         <v>2</v>
       </c>
-      <c r="B2">
-        <v>0.24299999999999999</v>
-      </c>
-      <c r="C2">
-        <v>0.25</v>
-      </c>
-      <c r="D2">
-        <v>0.24299999999999999</v>
-      </c>
-      <c r="E2">
-        <v>0.254</v>
-      </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3">
         <v>6</v>
       </c>
-      <c r="B3">
-        <v>0.246</v>
-      </c>
-      <c r="C3">
-        <v>0.253</v>
-      </c>
-      <c r="D3">
-        <v>0.247</v>
-      </c>
-      <c r="E3">
-        <v>0.25800000000000001</v>
-      </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4">
         <v>10</v>
       </c>
-      <c r="B4">
-        <v>0.246</v>
-      </c>
-      <c r="C4">
-        <v>0.25600000000000001</v>
-      </c>
-      <c r="D4">
-        <v>0.249</v>
-      </c>
-      <c r="E4">
-        <v>0.26200000000000001</v>
-      </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5">
         <v>14</v>
       </c>
-      <c r="B5">
-        <v>0.246</v>
-      </c>
-      <c r="C5">
-        <v>0.25900000000000001</v>
-      </c>
-      <c r="D5">
-        <v>0.25</v>
-      </c>
-      <c r="E5">
-        <v>0.26600000000000001</v>
-      </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6">
         <v>18</v>
       </c>
-      <c r="B6">
-        <v>0.247</v>
-      </c>
-      <c r="C6">
-        <v>0.26</v>
-      </c>
-      <c r="D6">
-        <v>0.252</v>
-      </c>
-      <c r="E6">
-        <v>0.26800000000000002</v>
-      </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7">
         <v>22</v>
       </c>
-      <c r="B7">
-        <v>0.248</v>
-      </c>
-      <c r="C7">
-        <v>0.26200000000000001</v>
-      </c>
-      <c r="D7">
-        <v>0.254</v>
-      </c>
-      <c r="E7">
-        <v>0.27100000000000002</v>
-      </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8">
         <v>26</v>
       </c>
-      <c r="B8">
-        <v>0.249</v>
-      </c>
-      <c r="C8">
-        <v>0.26300000000000001</v>
-      </c>
-      <c r="D8">
-        <v>0.255</v>
-      </c>
-      <c r="E8">
-        <v>0.27300000000000002</v>
-      </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9">
         <v>30</v>
-      </c>
-      <c r="B9">
-        <v>0.249</v>
-      </c>
-      <c r="C9">
-        <v>0.26400000000000001</v>
-      </c>
-      <c r="D9">
-        <v>0.25600000000000001</v>
-      </c>
-      <c r="E9">
-        <v>0.27500000000000002</v>
       </c>
     </row>
   </sheetData>
